--- a/docs/pension_data_combined_2026-10-22.xlsx
+++ b/docs/pension_data_combined_2026-10-22.xlsx
@@ -1353,9 +1353,6 @@
       <c r="C55" t="n">
         <v>1.185</v>
       </c>
-      <c r="D55" t="n">
-        <v>55914048.18</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/pension_data_combined_2026-10-22.xlsx
+++ b/docs/pension_data_combined_2026-10-22.xlsx
@@ -1353,6 +1353,9 @@
       <c r="C55" t="n">
         <v>1.185</v>
       </c>
+      <c r="D55" t="n">
+        <v>55914048.18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
